--- a/bdd/politecnicosanvalerobdd.xlsx
+++ b/bdd/politecnicosanvalerobdd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toshiba\Desktop\fundosvarepositoriosanvalero\bdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAF9A5A-43B7-4C3A-A9A9-E8750B57AC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0D2F71-DF78-4B11-8215-1B1D38A72E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{1929FC68-0D34-4BF3-B8F8-42762421600E}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t>id_usuario</t>
   </si>
@@ -205,6 +205,15 @@
   </si>
   <si>
     <t>Electronica_Digital</t>
+  </si>
+  <si>
+    <t>deurys_carvajal</t>
+  </si>
+  <si>
+    <t>deurys35@gmail.com</t>
+  </si>
+  <si>
+    <t>deurys1234</t>
   </si>
 </sst>
 </file>
@@ -281,7 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -304,6 +313,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -840,6 +852,26 @@
         <v>46275</v>
       </c>
     </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46277</v>
+      </c>
+    </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C9" s="7"/>
     </row>
@@ -851,9 +883,10 @@
     <hyperlink ref="C5" r:id="rId4" xr:uid="{912B5009-E223-4CF5-AF9F-7EBA61D06CE8}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{8325A2FE-52BA-4EE8-A3F6-3AC30E19D8FE}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{FF7576A3-6793-4A59-A5F0-9468C9815414}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{BD30D264-79CB-41D1-8C7C-DF44DBE5362B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
